--- a/data/trans_orig/IP16B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B01-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>39140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89788</t>
+          <t>89308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264198</t>
+          <t>264520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49785</t>
+          <t>49679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39725</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>47106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68995</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79295</t>
+          <t>79312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>26646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25464</t>
+          <t>25434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164724</t>
+          <t>165258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179957</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>32520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41676</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49761</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>21691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31612</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67099</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>113767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127644</t>
+          <t>127868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
